--- a/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Client/BulkDebtMailingReport.xlsx
+++ b/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Client/BulkDebtMailingReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lfey\source\repos\Vodovoz\Source\Libraries\Core\Business\Vodovoz.Reports\Reports\Client\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\VodovozSlot-1\Vodovoz\Source\Libraries\Core\Business\Vodovoz.Reports\Reports\Client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35A8A18-FBC7-4E43-B6AE-6B191CC41FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EC994D-50CF-4D97-834F-BA3577FBF618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="15900" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>{{SelectedFilters}}</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>Отчёт о рассылке писем о задолженности</t>
+  </si>
+  <si>
+    <t>Тип письма</t>
+  </si>
+  <si>
+    <t>{{item.EmailTypeString}}</t>
   </si>
 </sst>
 </file>
@@ -156,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -167,13 +173,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -494,41 +506,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AMF5"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="94.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="94.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="44.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" style="1" customWidth="1"/>
     <col min="9" max="1019" width="10.6640625" style="1"/>
-    <col min="1020" max="1020" width="14.77734375" style="2" customWidth="1"/>
-    <col min="1021" max="1024" width="14.77734375" customWidth="1"/>
+    <col min="1020" max="1020" width="14.83203125" style="2" customWidth="1"/>
+    <col min="1021" max="1024" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1020" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:1020" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:1020" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:1020" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1544,7 +1556,7 @@
       <c r="AMD2" s="1"/>
       <c r="AME2" s="1"/>
     </row>
-    <row r="3" spans="1:1020" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1020" ht="58.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1565,11 +1577,14 @@
       </c>
       <c r="G3" s="4" t="s">
         <v>6</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="AME3" s="2"/>
       <c r="AMF3"/>
     </row>
-    <row r="4" spans="1:1020" ht="11.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1020" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1590,11 +1605,14 @@
       </c>
       <c r="G4" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="AME4" s="2"/>
       <c r="AMF4"/>
     </row>
-    <row r="5" spans="1:1020" ht="11.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:1020" ht="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
